--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/91.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/91.xlsx
@@ -426,13 +426,13 @@
         <v>-10.70147487916866</v>
       </c>
       <c r="E2">
-        <v>-12.64588801192528</v>
+        <v>-13.45135862672159</v>
       </c>
       <c r="F2">
-        <v>-4.268347916102785</v>
+        <v>-5.12176597753035</v>
       </c>
       <c r="G2">
-        <v>-8.416036915148153</v>
+        <v>-7.543668439003724</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.17473273719208</v>
       </c>
       <c r="E3">
-        <v>-13.61962766389861</v>
+        <v>-14.24048145035021</v>
       </c>
       <c r="F3">
-        <v>-4.556452442061647</v>
+        <v>-5.133866768550446</v>
       </c>
       <c r="G3">
-        <v>-7.710003489078866</v>
+        <v>-7.680930278152986</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.542410500116029</v>
       </c>
       <c r="E4">
-        <v>-14.79801811322657</v>
+        <v>-14.48738291019642</v>
       </c>
       <c r="F4">
-        <v>-4.165245995680747</v>
+        <v>-5.249265803067042</v>
       </c>
       <c r="G4">
-        <v>-7.885581582299652</v>
+        <v>-7.501151102642864</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.864390100307835</v>
       </c>
       <c r="E5">
-        <v>-14.41666626009264</v>
+        <v>-15.8457349165892</v>
       </c>
       <c r="F5">
-        <v>-4.391145099893784</v>
+        <v>-5.094921903475229</v>
       </c>
       <c r="G5">
-        <v>-7.466668460305815</v>
+        <v>-7.336875211893149</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.133317824667964</v>
       </c>
       <c r="E6">
-        <v>-14.64720634334913</v>
+        <v>-16.30412969801564</v>
       </c>
       <c r="F6">
-        <v>-4.233289750881504</v>
+        <v>-5.110445508603692</v>
       </c>
       <c r="G6">
-        <v>-7.51365834369023</v>
+        <v>-6.706911501225235</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.359319546155946</v>
       </c>
       <c r="E7">
-        <v>-15.86666552345265</v>
+        <v>-17.39035664433949</v>
       </c>
       <c r="F7">
-        <v>-4.652859497134259</v>
+        <v>-5.159523792117354</v>
       </c>
       <c r="G7">
-        <v>-7.272816155708251</v>
+        <v>-6.492043853544378</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.551994826099202</v>
       </c>
       <c r="E8">
-        <v>-17.02305664605136</v>
+        <v>-17.83354933852218</v>
       </c>
       <c r="F8">
-        <v>-4.565781515751975</v>
+        <v>-5.088940262459614</v>
       </c>
       <c r="G8">
-        <v>-6.810697103881386</v>
+        <v>-6.64906633901755</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.719435811789451</v>
       </c>
       <c r="E9">
-        <v>-16.73106064203677</v>
+        <v>-18.77979662479493</v>
       </c>
       <c r="F9">
-        <v>-4.794173177480035</v>
+        <v>-5.359885157669485</v>
       </c>
       <c r="G9">
-        <v>-7.626951833135169</v>
+        <v>-6.496738207119065</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.865441647647107</v>
       </c>
       <c r="E10">
-        <v>-17.85955183627422</v>
+        <v>-19.05324852774811</v>
       </c>
       <c r="F10">
-        <v>-4.545831943590355</v>
+        <v>-5.350887430940277</v>
       </c>
       <c r="G10">
-        <v>-6.302448910510317</v>
+        <v>-5.234450366813736</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.016181296156539</v>
       </c>
       <c r="E11">
-        <v>-19.29776801026628</v>
+        <v>-20.04268387063202</v>
       </c>
       <c r="F11">
-        <v>-4.669609086018865</v>
+        <v>-5.335834338496604</v>
       </c>
       <c r="G11">
-        <v>-6.460186473819971</v>
+        <v>-5.702650890796241</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.189559196636262</v>
       </c>
       <c r="E12">
-        <v>-19.60363020169235</v>
+        <v>-21.44021170566516</v>
       </c>
       <c r="F12">
-        <v>-4.779332975458882</v>
+        <v>-5.446920892314226</v>
       </c>
       <c r="G12">
-        <v>-5.393465800701549</v>
+        <v>-5.405310932641061</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.40283712735078</v>
       </c>
       <c r="E13">
-        <v>-20.12722595188122</v>
+        <v>-21.25092602061855</v>
       </c>
       <c r="F13">
-        <v>-4.421286904579449</v>
+        <v>-5.396723484439382</v>
       </c>
       <c r="G13">
-        <v>-4.692454472215336</v>
+        <v>-4.660017747021556</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.688562071293838</v>
       </c>
       <c r="E14">
-        <v>-19.66058481928682</v>
+        <v>-22.05696269466582</v>
       </c>
       <c r="F14">
-        <v>-4.72744983991934</v>
+        <v>-4.781461879684077</v>
       </c>
       <c r="G14">
-        <v>-4.232444237896987</v>
+        <v>-4.356258641065729</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.065347342696665</v>
       </c>
       <c r="E15">
-        <v>-23.61561816336588</v>
+        <v>-22.63171208724533</v>
       </c>
       <c r="F15">
-        <v>-4.448130150267167</v>
+        <v>-4.780824865151324</v>
       </c>
       <c r="G15">
-        <v>-4.272448870193539</v>
+        <v>-3.876388444057291</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.5429681602934535</v>
       </c>
       <c r="E16">
-        <v>-22.35935154652801</v>
+        <v>-23.58278672681027</v>
       </c>
       <c r="F16">
-        <v>-3.906701760490785</v>
+        <v>-4.610197747522682</v>
       </c>
       <c r="G16">
-        <v>-3.929161850498814</v>
+        <v>-3.624055352508502</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.1357665066212345</v>
       </c>
       <c r="E17">
-        <v>-23.21996991778973</v>
+        <v>-24.04534770432376</v>
       </c>
       <c r="F17">
-        <v>-3.988492272741</v>
+        <v>-4.67272043398378</v>
       </c>
       <c r="G17">
-        <v>-3.340954050717727</v>
+        <v>-3.367405309576504</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.159180734063619</v>
       </c>
       <c r="E18">
-        <v>-23.24144847000811</v>
+        <v>-25.77395680253169</v>
       </c>
       <c r="F18">
-        <v>-3.599373312215155</v>
+        <v>-4.03803444200023</v>
       </c>
       <c r="G18">
-        <v>-3.870863143552248</v>
+        <v>-3.167034540812115</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.3553763936036164</v>
       </c>
       <c r="E19">
-        <v>-25.08224145480806</v>
+        <v>-26.26881938514189</v>
       </c>
       <c r="F19">
-        <v>-3.149213614511819</v>
+        <v>-4.149565829113155</v>
       </c>
       <c r="G19">
-        <v>-3.389331052683097</v>
+        <v>-3.655558503860207</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.4638983823362555</v>
       </c>
       <c r="E20">
-        <v>-26.02392403928108</v>
+        <v>-26.50384718613998</v>
       </c>
       <c r="F20">
-        <v>-3.188035052844018</v>
+        <v>-3.712566404338096</v>
       </c>
       <c r="G20">
-        <v>-2.917085042051601</v>
+        <v>-2.499108804445378</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5048218014794099</v>
       </c>
       <c r="E21">
-        <v>-26.88327896629466</v>
+        <v>-27.85848584384647</v>
       </c>
       <c r="F21">
-        <v>-2.80480661291948</v>
+        <v>-3.469961614712802</v>
       </c>
       <c r="G21">
-        <v>-3.174791149010627</v>
+        <v>-2.600232728487956</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.4995913896494155</v>
       </c>
       <c r="E22">
-        <v>-27.14572214893519</v>
+        <v>-27.83313091787753</v>
       </c>
       <c r="F22">
-        <v>-2.665354274127794</v>
+        <v>-3.104799039475918</v>
       </c>
       <c r="G22">
-        <v>-2.439896386929973</v>
+        <v>-3.371788471870499</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.4617457583159907</v>
       </c>
       <c r="E23">
-        <v>-27.43193982011599</v>
+        <v>-27.67846541661956</v>
       </c>
       <c r="F23">
-        <v>-2.582280620770643</v>
+        <v>-2.556692351698166</v>
       </c>
       <c r="G23">
-        <v>-2.49514608143487</v>
+        <v>-2.131754118680151</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.404246083174437</v>
       </c>
       <c r="E24">
-        <v>-27.75995983486159</v>
+        <v>-29.46776738771529</v>
       </c>
       <c r="F24">
-        <v>-2.468183779811247</v>
+        <v>-2.594592645478452</v>
       </c>
       <c r="G24">
-        <v>-2.449626080269891</v>
+        <v>-3.13398867523911</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.3362025688134614</v>
       </c>
       <c r="E25">
-        <v>-28.64797547386972</v>
+        <v>-28.99042773527777</v>
       </c>
       <c r="F25">
-        <v>-2.27067862506397</v>
+        <v>-2.387170276184859</v>
       </c>
       <c r="G25">
-        <v>-3.042965225636849</v>
+        <v>-2.57732044281066</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.2616563843079484</v>
       </c>
       <c r="E26">
-        <v>-28.88990919772951</v>
+        <v>-29.24255958260283</v>
       </c>
       <c r="F26">
-        <v>-2.16315239434358</v>
+        <v>-2.434216574459454</v>
       </c>
       <c r="G26">
-        <v>-2.206324156952234</v>
+        <v>-2.68088423891568</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.1842329459562344</v>
       </c>
       <c r="E27">
-        <v>-28.00163543570294</v>
+        <v>-29.42860061602294</v>
       </c>
       <c r="F27">
-        <v>-1.616127554393884</v>
+        <v>-1.910262595045127</v>
       </c>
       <c r="G27">
-        <v>-3.388731843940489</v>
+        <v>-3.557083016249046</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.1059011246650418</v>
       </c>
       <c r="E28">
-        <v>-28.54747505021749</v>
+        <v>-29.12349241551915</v>
       </c>
       <c r="F28">
-        <v>-2.088022784379276</v>
+        <v>-2.458689861007763</v>
       </c>
       <c r="G28">
-        <v>-3.414054206770374</v>
+        <v>-3.090630460311275</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.02806076044699468</v>
       </c>
       <c r="E29">
-        <v>-29.89755353459826</v>
+        <v>-29.0056207655735</v>
       </c>
       <c r="F29">
-        <v>-1.904305805051596</v>
+        <v>-2.412778426075003</v>
       </c>
       <c r="G29">
-        <v>-3.44036973326204</v>
+        <v>-2.926831288119216</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.0474941122776491</v>
       </c>
       <c r="E30">
-        <v>-28.21977202865243</v>
+        <v>-28.80190736233845</v>
       </c>
       <c r="F30">
-        <v>-1.479624203556165</v>
+        <v>-2.337877445513871</v>
       </c>
       <c r="G30">
-        <v>-4.074498110218358</v>
+        <v>-3.783474672952106</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.119814295754864</v>
       </c>
       <c r="E31">
-        <v>-28.15784967507154</v>
+        <v>-28.22502958697533</v>
       </c>
       <c r="F31">
-        <v>-1.517782947966124</v>
+        <v>-2.17093739119509</v>
       </c>
       <c r="G31">
-        <v>-3.66453670336271</v>
+        <v>-4.636012981316301</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.1869581512890216</v>
       </c>
       <c r="E32">
-        <v>-27.6160902156379</v>
+        <v>-29.37389891424729</v>
       </c>
       <c r="F32">
-        <v>-1.731693090758443</v>
+        <v>-2.0720808537124</v>
       </c>
       <c r="G32">
-        <v>-3.370974077667838</v>
+        <v>-4.040339901344158</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.2469065331979624</v>
       </c>
       <c r="E33">
-        <v>-27.47946615482649</v>
+        <v>-27.46210398548108</v>
       </c>
       <c r="F33">
-        <v>-1.948786649479721</v>
+        <v>-2.261494515669132</v>
       </c>
       <c r="G33">
-        <v>-3.328638821311638</v>
+        <v>-4.227590978136415</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.2984183232253032</v>
       </c>
       <c r="E34">
-        <v>-27.50107603279109</v>
+        <v>-28.18424162158824</v>
       </c>
       <c r="F34">
-        <v>-2.285900704457814</v>
+        <v>-2.22369611107939</v>
       </c>
       <c r="G34">
-        <v>-3.934975168465774</v>
+        <v>-4.537415003520187</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.3398613416427013</v>
       </c>
       <c r="E35">
-        <v>-26.777208519613</v>
+        <v>-27.21410210645102</v>
       </c>
       <c r="F35">
-        <v>-2.032377204096219</v>
+        <v>-2.436464763590652</v>
       </c>
       <c r="G35">
-        <v>-4.142145797767825</v>
+        <v>-3.422264359707766</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.370333942660732</v>
       </c>
       <c r="E36">
-        <v>-27.27097068303934</v>
+        <v>-27.21383492648456</v>
       </c>
       <c r="F36">
-        <v>-2.325122244245565</v>
+        <v>-2.352293523424791</v>
       </c>
       <c r="G36">
-        <v>-2.923328730938667</v>
+        <v>-4.343817610929148</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.390066265210502</v>
       </c>
       <c r="E37">
-        <v>-25.74071327484138</v>
+        <v>-26.24116852285105</v>
       </c>
       <c r="F37">
-        <v>-2.107418178748424</v>
+        <v>-2.262061118972647</v>
       </c>
       <c r="G37">
-        <v>-3.981240042377089</v>
+        <v>-4.406042624885289</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.4000523292523359</v>
       </c>
       <c r="E38">
-        <v>-24.11295329278427</v>
+        <v>-25.66555872021008</v>
       </c>
       <c r="F38">
-        <v>-2.068976132686707</v>
+        <v>-2.171272051625821</v>
       </c>
       <c r="G38">
-        <v>-4.704564447797989</v>
+        <v>-3.624445996882137</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.4013815980226338</v>
       </c>
       <c r="E39">
-        <v>-24.80546112345924</v>
+        <v>-26.2834055999206</v>
       </c>
       <c r="F39">
-        <v>-2.223963673750494</v>
+        <v>-2.062253102845586</v>
       </c>
       <c r="G39">
-        <v>-3.672968662851234</v>
+        <v>-4.002861215294069</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.3955647568286051</v>
       </c>
       <c r="E40">
-        <v>-23.3933516021214</v>
+        <v>-25.23115126560228</v>
       </c>
       <c r="F40">
-        <v>-1.992756391220319</v>
+        <v>-2.411513509050928</v>
       </c>
       <c r="G40">
-        <v>-3.408787128817393</v>
+        <v>-4.24610023824648</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.3842552361331111</v>
       </c>
       <c r="E41">
-        <v>-22.68806894627079</v>
+        <v>-23.71877680126061</v>
       </c>
       <c r="F41">
-        <v>-2.184810888457176</v>
+        <v>-2.471761498623938</v>
       </c>
       <c r="G41">
-        <v>-3.77073900426253</v>
+        <v>-3.934885783736213</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3689554067153397</v>
       </c>
       <c r="E42">
-        <v>-22.89285559784566</v>
+        <v>-23.40573245005837</v>
       </c>
       <c r="F42">
-        <v>-2.331852729393311</v>
+        <v>-2.463781007065368</v>
       </c>
       <c r="G42">
-        <v>-3.21411711947163</v>
+        <v>-3.76092654728413</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.352767342255881</v>
       </c>
       <c r="E43">
-        <v>-23.22476557176385</v>
+        <v>-23.48907901416955</v>
       </c>
       <c r="F43">
-        <v>-2.799202707439541</v>
+        <v>-2.603882785900848</v>
       </c>
       <c r="G43">
-        <v>-3.318296677046955</v>
+        <v>-3.383951416181781</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.3389276009096666</v>
       </c>
       <c r="E44">
-        <v>-21.76469045373677</v>
+        <v>-23.52373995422425</v>
       </c>
       <c r="F44">
-        <v>-2.415521978913075</v>
+        <v>-2.753923316835117</v>
       </c>
       <c r="G44">
-        <v>-3.215113593678951</v>
+        <v>-3.537696461571074</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.3301231280524332</v>
       </c>
       <c r="E45">
-        <v>-20.53293646670241</v>
+        <v>-22.10926656945441</v>
       </c>
       <c r="F45">
-        <v>-2.33374057870429</v>
+        <v>-2.561761131835897</v>
       </c>
       <c r="G45">
-        <v>-2.677120148637529</v>
+        <v>-4.039095136221392</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.3305905957112645</v>
       </c>
       <c r="E46">
-        <v>-20.86116931972638</v>
+        <v>-21.13979726847032</v>
       </c>
       <c r="F46">
-        <v>-2.554029150498166</v>
+        <v>-2.838693466633202</v>
       </c>
       <c r="G46">
-        <v>-3.447586722537652</v>
+        <v>-2.854525662995993</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.3452529793242455</v>
       </c>
       <c r="E47">
-        <v>-18.62320199360969</v>
+        <v>-21.07209658205565</v>
       </c>
       <c r="F47">
-        <v>-2.188609781366414</v>
+        <v>-2.983760479681063</v>
       </c>
       <c r="G47">
-        <v>-3.467939956513091</v>
+        <v>-3.583143630734189</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.3770573413810226</v>
       </c>
       <c r="E48">
-        <v>-20.08637911633203</v>
+        <v>-21.39968186329651</v>
       </c>
       <c r="F48">
-        <v>-2.008251831857086</v>
+        <v>-2.777950113353317</v>
       </c>
       <c r="G48">
-        <v>-3.755172819136877</v>
+        <v>-3.762121654223807</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.4297498164709153</v>
       </c>
       <c r="E49">
-        <v>-18.25813453300734</v>
+        <v>-19.5850634582609</v>
       </c>
       <c r="F49">
-        <v>-2.255920431415694</v>
+        <v>-2.957207990951727</v>
       </c>
       <c r="G49">
-        <v>-2.687876111094621</v>
+        <v>-3.374211791205245</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.5060644196921348</v>
       </c>
       <c r="E50">
-        <v>-17.57041782783248</v>
+        <v>-18.15279769911492</v>
       </c>
       <c r="F50">
-        <v>-2.212710302583463</v>
+        <v>-2.968372726806659</v>
       </c>
       <c r="G50">
-        <v>-4.381968337723709</v>
+        <v>-3.858743236332976</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.6056204877673915</v>
       </c>
       <c r="E51">
-        <v>-17.43804147564026</v>
+        <v>-18.58649871177753</v>
       </c>
       <c r="F51">
-        <v>-2.518414322382204</v>
+        <v>-2.830167080956187</v>
       </c>
       <c r="G51">
-        <v>-3.708391500121436</v>
+        <v>-3.820410429533755</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.7298733282101263</v>
       </c>
       <c r="E52">
-        <v>-15.32460265626051</v>
+        <v>-17.89706571495376</v>
       </c>
       <c r="F52">
-        <v>-2.101651084890134</v>
+        <v>-3.157821180194309</v>
       </c>
       <c r="G52">
-        <v>-3.419334526905511</v>
+        <v>-4.070734019940207</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.8802538012229641</v>
       </c>
       <c r="E53">
-        <v>-15.76702098138788</v>
+        <v>-17.40255635331616</v>
       </c>
       <c r="F53">
-        <v>-2.630726031588567</v>
+        <v>-2.79934435826542</v>
       </c>
       <c r="G53">
-        <v>-4.382805905745144</v>
+        <v>-4.155046993734365</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.054983872124738</v>
       </c>
       <c r="E54">
-        <v>-15.81627719316931</v>
+        <v>-17.1787682248051</v>
       </c>
       <c r="F54">
-        <v>-2.400622962806322</v>
+        <v>-2.910237074110787</v>
       </c>
       <c r="G54">
-        <v>-4.065500047442619</v>
+        <v>-4.262010720108218</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.253828559012802</v>
       </c>
       <c r="E55">
-        <v>-15.68493333305084</v>
+        <v>-16.37234210199317</v>
       </c>
       <c r="F55">
-        <v>-2.406999735073073</v>
+        <v>-3.270474176770624</v>
       </c>
       <c r="G55">
-        <v>-3.620261467320498</v>
+        <v>-4.561201273219851</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.47594470211002</v>
       </c>
       <c r="E56">
-        <v>-13.71683588694726</v>
+        <v>-15.93674818719536</v>
       </c>
       <c r="F56">
-        <v>-2.368197349191139</v>
+        <v>-3.036500975482502</v>
       </c>
       <c r="G56">
-        <v>-4.317727201534152</v>
+        <v>-4.450019911828967</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.716525844825673</v>
       </c>
       <c r="E57">
-        <v>-14.29212416793369</v>
+        <v>-15.4296858956085</v>
       </c>
       <c r="F57">
-        <v>-2.446924558785801</v>
+        <v>-3.326179399506683</v>
       </c>
       <c r="G57">
-        <v>-4.846530572158556</v>
+        <v>-4.714764238604484</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.972052817801711</v>
       </c>
       <c r="E58">
-        <v>-13.60208435559289</v>
+        <v>-15.67713982928364</v>
       </c>
       <c r="F58">
-        <v>-2.35087287332899</v>
+        <v>-3.113227677799403</v>
       </c>
       <c r="G58">
-        <v>-4.637909923910303</v>
+        <v>-4.49702303739554</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.239257131977842</v>
       </c>
       <c r="E59">
-        <v>-12.83500614343361</v>
+        <v>-14.28391404455778</v>
       </c>
       <c r="F59">
-        <v>-2.341273751865349</v>
+        <v>-3.391537587587564</v>
       </c>
       <c r="G59">
-        <v>-4.967286031249012</v>
+        <v>-4.653419829761789</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.510851028245067</v>
       </c>
       <c r="E60">
-        <v>-13.17019020405935</v>
+        <v>-14.54052455267643</v>
       </c>
       <c r="F60">
-        <v>-2.795887581093537</v>
+        <v>-3.265367291732366</v>
       </c>
       <c r="G60">
-        <v>-5.587096298747981</v>
+        <v>-4.948114662031093</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.779548678722842</v>
       </c>
       <c r="E61">
-        <v>-12.2607322406249</v>
+        <v>-13.33589159647402</v>
       </c>
       <c r="F61">
-        <v>-2.441820987217153</v>
+        <v>-3.212630109400538</v>
       </c>
       <c r="G61">
-        <v>-5.919388996706787</v>
+        <v>-5.043402094287935</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.038538711061754</v>
       </c>
       <c r="E62">
-        <v>-12.24108772037963</v>
+        <v>-13.78069642740343</v>
       </c>
       <c r="F62">
-        <v>-2.710161495312622</v>
+        <v>-3.355913647430171</v>
       </c>
       <c r="G62">
-        <v>-5.976853446177456</v>
+        <v>-5.590482986834655</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.27885079678421</v>
       </c>
       <c r="E63">
-        <v>-12.42784651692996</v>
+        <v>-13.58413348462649</v>
       </c>
       <c r="F63">
-        <v>-3.088958997999586</v>
+        <v>-3.343482337816359</v>
       </c>
       <c r="G63">
-        <v>-5.981739811393421</v>
+        <v>-6.178776860799763</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.492358102702547</v>
       </c>
       <c r="E64">
-        <v>-12.74033839430326</v>
+        <v>-12.09595918538181</v>
       </c>
       <c r="F64">
-        <v>-2.739095540325006</v>
+        <v>-3.570441752304979</v>
       </c>
       <c r="G64">
-        <v>-5.656045030694382</v>
+        <v>-6.132326596338249</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.673534986426235</v>
       </c>
       <c r="E65">
-        <v>-10.90049638904493</v>
+        <v>-12.65780695551347</v>
       </c>
       <c r="F65">
-        <v>-2.65013219473395</v>
+        <v>-3.232159699288939</v>
       </c>
       <c r="G65">
-        <v>-6.287412412670947</v>
+        <v>-5.580250090572768</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.81747883942172</v>
       </c>
       <c r="E66">
-        <v>-11.80999963721945</v>
+        <v>-13.35416851756897</v>
       </c>
       <c r="F66">
-        <v>-2.982662064504951</v>
+        <v>-3.578168763438293</v>
       </c>
       <c r="G66">
-        <v>-5.456432376858487</v>
+        <v>-6.034079536369299</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.920861553727882</v>
       </c>
       <c r="E67">
-        <v>-10.79988275354251</v>
+        <v>-12.17033031400978</v>
       </c>
       <c r="F67">
-        <v>-2.995100001057985</v>
+        <v>-3.411231194221719</v>
       </c>
       <c r="G67">
-        <v>-6.095933769225041</v>
+        <v>-5.337381848720756</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.98345036184848</v>
       </c>
       <c r="E68">
-        <v>-11.40965989257135</v>
+        <v>-11.89351828334291</v>
       </c>
       <c r="F68">
-        <v>-3.326190996650322</v>
+        <v>-3.560574239802831</v>
       </c>
       <c r="G68">
-        <v>-6.851814079479134</v>
+        <v>-5.603890696268704</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.006501158969655</v>
       </c>
       <c r="E69">
-        <v>-10.84192963470373</v>
+        <v>-13.04597869050296</v>
       </c>
       <c r="F69">
-        <v>-2.872186845830595</v>
+        <v>-3.652301019049626</v>
       </c>
       <c r="G69">
-        <v>-5.111874107676681</v>
+        <v>-6.249556324429381</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.991140323587548</v>
       </c>
       <c r="E70">
-        <v>-10.73661544318134</v>
+        <v>-12.99465296610002</v>
       </c>
       <c r="F70">
-        <v>-2.829429005600292</v>
+        <v>-3.615763389646945</v>
       </c>
       <c r="G70">
-        <v>-6.883135150826179</v>
+        <v>-5.999586962395631</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.93975511702438</v>
       </c>
       <c r="E71">
-        <v>-10.07731944087863</v>
+        <v>-12.22598073109004</v>
       </c>
       <c r="F71">
-        <v>-3.311644865057163</v>
+        <v>-3.64230676633485</v>
       </c>
       <c r="G71">
-        <v>-6.990747744125729</v>
+        <v>-6.398365346419621</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.856875132994794</v>
       </c>
       <c r="E72">
-        <v>-10.69330058929798</v>
+        <v>-11.82455868115411</v>
       </c>
       <c r="F72">
-        <v>-3.134051177570977</v>
+        <v>-3.747791071407339</v>
       </c>
       <c r="G72">
-        <v>-6.225551558724126</v>
+        <v>-5.912840737630109</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.745137281714022</v>
       </c>
       <c r="E73">
-        <v>-11.6801456450495</v>
+        <v>-12.47165950295417</v>
       </c>
       <c r="F73">
-        <v>-3.702299618747798</v>
+        <v>-3.650962377326702</v>
       </c>
       <c r="G73">
-        <v>-6.411961756949408</v>
+        <v>-6.107623305524208</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.606671010940468</v>
       </c>
       <c r="E74">
-        <v>-12.193484401611</v>
+        <v>-12.54524267710481</v>
       </c>
       <c r="F74">
-        <v>-3.204585005184549</v>
+        <v>-3.913718032392497</v>
       </c>
       <c r="G74">
-        <v>-5.669929458686085</v>
+        <v>-5.707884863293829</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.445952193233801</v>
       </c>
       <c r="E75">
-        <v>-12.06786000416422</v>
+        <v>-12.72709260783083</v>
       </c>
       <c r="F75">
-        <v>-3.379808733531326</v>
+        <v>-3.995578127504547</v>
       </c>
       <c r="G75">
-        <v>-5.249126015189325</v>
+        <v>-5.75189856623844</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.264075532590458</v>
       </c>
       <c r="E76">
-        <v>-12.45122249975756</v>
+        <v>-12.35966128379647</v>
       </c>
       <c r="F76">
-        <v>-3.273805042097282</v>
+        <v>-3.963714975355864</v>
       </c>
       <c r="G76">
-        <v>-6.267794119805226</v>
+        <v>-4.89384488900582</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.060738424860984</v>
       </c>
       <c r="E77">
-        <v>-12.21459614743476</v>
+        <v>-13.56744152943422</v>
       </c>
       <c r="F77">
-        <v>-3.657301044692924</v>
+        <v>-4.343607579749328</v>
       </c>
       <c r="G77">
-        <v>-5.559380411493203</v>
+        <v>-5.296317841851636</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.839853813706056</v>
       </c>
       <c r="E78">
-        <v>-13.31840262985639</v>
+        <v>-13.63451275796182</v>
       </c>
       <c r="F78">
-        <v>-3.413072654958143</v>
+        <v>-4.093958353730627</v>
       </c>
       <c r="G78">
-        <v>-4.725391089785544</v>
+        <v>-4.469512403964196</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.604011354413744</v>
       </c>
       <c r="E79">
-        <v>-14.46248988857625</v>
+        <v>-14.68156387564532</v>
       </c>
       <c r="F79">
-        <v>-3.566328079782676</v>
+        <v>-4.352643411379066</v>
       </c>
       <c r="G79">
-        <v>-4.74335410988163</v>
+        <v>-4.402291776789294</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.355661826000577</v>
       </c>
       <c r="E80">
-        <v>-14.35637868562852</v>
+        <v>-14.43739308562574</v>
       </c>
       <c r="F80">
-        <v>-3.949746215842456</v>
+        <v>-4.537617852424195</v>
       </c>
       <c r="G80">
-        <v>-4.728234848403779</v>
+        <v>-4.842849245518886</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.102333806857888</v>
       </c>
       <c r="E81">
-        <v>-14.56651346500645</v>
+        <v>-15.897572358555</v>
       </c>
       <c r="F81">
-        <v>-3.703061716758374</v>
+        <v>-4.167601044206906</v>
       </c>
       <c r="G81">
-        <v>-4.117204147674956</v>
+        <v>-4.388483491344994</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.850630974716361</v>
       </c>
       <c r="E82">
-        <v>-15.65529447067063</v>
+        <v>-16.31436404927297</v>
       </c>
       <c r="F82">
-        <v>-4.204503983634221</v>
+        <v>-4.251293488013949</v>
       </c>
       <c r="G82">
-        <v>-4.306060839053759</v>
+        <v>-4.232536933172086</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.607632053026552</v>
       </c>
       <c r="E83">
-        <v>-16.72178179879506</v>
+        <v>-17.18098264859485</v>
       </c>
       <c r="F83">
-        <v>-3.605422050990396</v>
+        <v>-4.532438899421892</v>
       </c>
       <c r="G83">
-        <v>-4.638704454839728</v>
+        <v>-3.725050165275048</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.384398034394746</v>
       </c>
       <c r="E84">
-        <v>-18.54435673266214</v>
+        <v>-18.00605249889636</v>
       </c>
       <c r="F84">
-        <v>-4.329700119423728</v>
+        <v>-4.821287299308469</v>
       </c>
       <c r="G84">
-        <v>-4.15320633041453</v>
+        <v>-3.306683283295191</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.189152129228701</v>
       </c>
       <c r="E85">
-        <v>-17.52244317419522</v>
+        <v>-19.27559207305072</v>
       </c>
       <c r="F85">
-        <v>-3.992875993036615</v>
+        <v>-4.659917187406111</v>
       </c>
       <c r="G85">
-        <v>-4.234132616122015</v>
+        <v>-3.838108605986699</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.029982080535662</v>
       </c>
       <c r="E86">
-        <v>-19.00676827053338</v>
+        <v>-20.25711617184323</v>
       </c>
       <c r="F86">
-        <v>-3.670846508463501</v>
+        <v>-5.006340435256864</v>
       </c>
       <c r="G86">
-        <v>-3.578392997885335</v>
+        <v>-3.621423468804782</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.9174614311812198</v>
       </c>
       <c r="E87">
-        <v>-19.30868163262477</v>
+        <v>-20.85609742883778</v>
       </c>
       <c r="F87">
-        <v>-4.44376962425883</v>
+        <v>-4.711038224935077</v>
       </c>
       <c r="G87">
-        <v>-3.504879023640279</v>
+        <v>-3.051354148033362</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.8589261296356293</v>
       </c>
       <c r="E88">
-        <v>-21.21968407843963</v>
+        <v>-23.47078850765257</v>
       </c>
       <c r="F88">
-        <v>-4.099558117373552</v>
+        <v>-4.664054054215692</v>
       </c>
       <c r="G88">
-        <v>-3.411650750708863</v>
+        <v>-3.012759808136539</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8628665396167935</v>
       </c>
       <c r="E89">
-        <v>-23.09934495564741</v>
+        <v>-23.15511764152588</v>
       </c>
       <c r="F89">
-        <v>-4.157692941702021</v>
+        <v>-4.86550058106549</v>
       </c>
       <c r="G89">
-        <v>-3.484128524200127</v>
+        <v>-3.154139965936654</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.9369369471132512</v>
       </c>
       <c r="E90">
-        <v>-23.0097173980876</v>
+        <v>-25.74188162113536</v>
       </c>
       <c r="F90">
-        <v>-4.50869540455545</v>
+        <v>-4.886547740035819</v>
       </c>
       <c r="G90">
-        <v>-2.559109131799129</v>
+        <v>-2.328175406616189</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.081749200368458</v>
       </c>
       <c r="E91">
-        <v>-24.63974161714854</v>
+        <v>-26.82588055824744</v>
       </c>
       <c r="F91">
-        <v>-4.106205765781018</v>
+        <v>-5.182906947163579</v>
       </c>
       <c r="G91">
-        <v>-2.967706593892597</v>
+        <v>-3.856710561371864</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.298128649644118</v>
       </c>
       <c r="E92">
-        <v>-27.60009111696881</v>
+        <v>-28.19492429177234</v>
       </c>
       <c r="F92">
-        <v>-3.87086410154347</v>
+        <v>-5.315104444241546</v>
       </c>
       <c r="G92">
-        <v>-2.45322133272554</v>
+        <v>-3.363098289829912</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.581869217356542</v>
       </c>
       <c r="E93">
-        <v>-28.39655459696386</v>
+        <v>-30.17206962894324</v>
       </c>
       <c r="F93">
-        <v>-4.371699175113065</v>
+        <v>-5.39754853837257</v>
       </c>
       <c r="G93">
-        <v>-3.677497489148957</v>
+        <v>-3.400030735866021</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.919451884674043</v>
       </c>
       <c r="E94">
-        <v>-31.07195213408846</v>
+        <v>-32.3948507174752</v>
       </c>
       <c r="F94">
-        <v>-4.969991673622022</v>
+        <v>-5.316916912118872</v>
       </c>
       <c r="G94">
-        <v>-3.577754062596255</v>
+        <v>-3.699141835884712</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.298660465517256</v>
       </c>
       <c r="E95">
-        <v>-33.37005533079</v>
+        <v>-34.96602995378728</v>
       </c>
       <c r="F95">
-        <v>-4.639261846217305</v>
+        <v>-5.600514291039102</v>
       </c>
       <c r="G95">
-        <v>-4.348134562312358</v>
+        <v>-4.030669797823947</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.704644709004137</v>
       </c>
       <c r="E96">
-        <v>-35.06645565761838</v>
+        <v>-35.70380893911693</v>
       </c>
       <c r="F96">
-        <v>-4.722226155077287</v>
+        <v>-5.408411748492883</v>
       </c>
       <c r="G96">
-        <v>-4.09252072013415</v>
+        <v>-4.439273881008493</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.113029108324834</v>
       </c>
       <c r="E97">
-        <v>-36.98563879172811</v>
+        <v>-38.03926072519673</v>
       </c>
       <c r="F97">
-        <v>-5.050544604972455</v>
+        <v>-5.523639310957099</v>
       </c>
       <c r="G97">
-        <v>-3.991519286276525</v>
+        <v>-4.722265934796472</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.508208389480896</v>
       </c>
       <c r="E98">
-        <v>-38.96698202430412</v>
+        <v>-40.79863881279358</v>
       </c>
       <c r="F98">
-        <v>-5.249426506343185</v>
+        <v>-5.483292848236347</v>
       </c>
       <c r="G98">
-        <v>-5.337567239270955</v>
+        <v>-5.335018119205716</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.866210774432271</v>
       </c>
       <c r="E99">
-        <v>-41.05338132538407</v>
+        <v>-42.51775396524444</v>
       </c>
       <c r="F99">
-        <v>-5.450205369066326</v>
+        <v>-5.793957132043051</v>
       </c>
       <c r="G99">
-        <v>-6.476729269879709</v>
+        <v>-5.698261107411168</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.175927931089017</v>
       </c>
       <c r="E100">
-        <v>-43.50041018253886</v>
+        <v>-43.99791739396954</v>
       </c>
       <c r="F100">
-        <v>-5.003499135065262</v>
+        <v>-5.942457727975516</v>
       </c>
       <c r="G100">
-        <v>-5.950143964766617</v>
+        <v>-5.887677280986108</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.413861849589085</v>
       </c>
       <c r="E101">
-        <v>-45.95390570057661</v>
+        <v>-46.4821204942533</v>
       </c>
       <c r="F101">
-        <v>-5.364978788829299</v>
+        <v>-5.932149524015078</v>
       </c>
       <c r="G101">
-        <v>-5.764902389116697</v>
+        <v>-6.115899669372386</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.595701319922016</v>
       </c>
       <c r="E102">
-        <v>-48.38803972799456</v>
+        <v>-48.57401736277857</v>
       </c>
       <c r="F102">
-        <v>-5.443276904109311</v>
+        <v>-5.892510487056317</v>
       </c>
       <c r="G102">
-        <v>-5.646235884261522</v>
+        <v>-6.46959173369704</v>
       </c>
     </row>
   </sheetData>
